--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -894,10 +894,10 @@
         <v>9</v>
       </c>
       <c r="G13" t="n">
-        <v>4.22</v>
+        <v>9.52</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.78</v>
+        <v>0.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>3.95</v>
+        <v>7.63</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.05</v>
+        <v>-1.37</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>59.11</v>
+        <v>64.41</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.89</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="3">
@@ -1410,10 +1410,10 @@
         <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>70.48</v>
+        <v>74.16</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.52</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>341</v>
+        <v>1023</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>342</v>
+        <v>1024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>343</v>
+        <v>1025</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>344</v>
+        <v>1026</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>345</v>
+        <v>1027</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>346</v>
+        <v>1028</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>347</v>
+        <v>1029</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>348</v>
+        <v>1030</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>349</v>
+        <v>1031</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>350</v>
+        <v>1032</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>351</v>
+        <v>1033</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>352</v>
+        <v>1034</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1302</v>
+        <v>1035</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.65</v>
+        <v>-0.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1303</v>
+        <v>1036</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:30 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1304</v>
+        <v>1037</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:30 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,34 +1030,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1305</v>
+        <v>1038</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1060,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1306</v>
+        <v>1039</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1307</v>
+        <v>1040</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>9.779999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="H19" t="n">
-        <v>0.78</v>
+        <v>-1.08</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1308</v>
+        <v>1041</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1309</v>
+        <v>1042</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>10.35</v>
+        <v>4.77</v>
       </c>
       <c r="H21" t="n">
-        <v>1.35</v>
+        <v>-4.23</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1310</v>
+        <v>3782</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1218,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1311</v>
+        <v>3783</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1258,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1312</v>
+        <v>3784</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1288,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1313</v>
+        <v>3785</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,33 +1318,623 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3786</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3787</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3788</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3790</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3791</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3792</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3793</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>08:30 AM</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>06:00 PM</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" t="n">
         <v>7.63</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H33" t="n">
         <v>-1.37</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3794</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3796</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3797</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3798</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3799</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3801</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -1391,13 +1981,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>64.41</v>
+        <v>110.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.59</v>
+        <v>-15.3</v>
       </c>
     </row>
     <row r="3">
@@ -1407,13 +1997,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>74.16</v>
+        <v>122.82</v>
       </c>
       <c r="D3" t="n">
-        <v>2.16</v>
+        <v>2.82</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1023</v>
+        <v>341</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1024</v>
+        <v>342</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1025</v>
+        <v>343</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1026</v>
+        <v>344</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1027</v>
+        <v>345</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1028</v>
+        <v>346</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1029</v>
+        <v>347</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1030</v>
+        <v>348</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1031</v>
+        <v>349</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1032</v>
+        <v>350</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1033</v>
+        <v>351</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1034</v>
+        <v>352</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1035</v>
+        <v>1302</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>09:30 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.1</v>
+        <v>8.35</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9</v>
+        <v>-0.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,34 +950,24 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1036</v>
+        <v>1303</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>09:30 AM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -990,34 +980,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1037</v>
+        <v>1304</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>09:30 AM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>07:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9.220000000000001</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1030,24 +1010,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1038</v>
+        <v>1305</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46158</v>
+        <v>46146</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1060,24 +1050,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1039</v>
+        <v>1306</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46159</v>
+        <v>46147</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1040</v>
+        <v>1307</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>09:30 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>7.92</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.08</v>
+        <v>0.78</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1041</v>
+        <v>1308</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>09:30 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1042</v>
+        <v>1309</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIAZ, MARLENE A [6510]</t>
+          <t>ZHANG, CECILIA [6608]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09:30 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07:00 PM</t>
+          <t>06:00 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>4.77</v>
+        <v>10.35</v>
       </c>
       <c r="H21" t="n">
-        <v>-4.23</v>
+        <v>1.35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3782</v>
+        <v>1310</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,26 +1218,16 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1240,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3783</v>
+        <v>1311</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,7 +1248,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1280,7 +1270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3784</v>
+        <v>1312</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,16 +1278,26 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3785</v>
+        <v>1313</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1334,10 @@
         <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.75</v>
+        <v>7.63</v>
       </c>
       <c r="H25" t="n">
-        <v>0.75</v>
+        <v>-1.37</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1345,596 +1345,6 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>3786</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>9</v>
-      </c>
-      <c r="G26" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>3787</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>9</v>
-      </c>
-      <c r="G27" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>3788</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>9</v>
-      </c>
-      <c r="G28" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>3789</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>9</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>3790</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>3791</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>3792</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>9</v>
-      </c>
-      <c r="G32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>3793</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>9</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-1.37</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>3794</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>9</v>
-      </c>
-      <c r="G34" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>3795</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>9</v>
-      </c>
-      <c r="G35" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>3796</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="H36" t="n">
-        <v>6.08</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>3797</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>3798</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>3799</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>3800</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>9</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>8611</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>3801</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-4.83</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -1981,13 +1391,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>110.7</v>
+        <v>64.41</v>
       </c>
       <c r="D2" t="n">
-        <v>-15.3</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +1407,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>122.82</v>
+        <v>74.16</v>
       </c>
       <c r="D3" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>341</v>
+        <v>1023</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>342</v>
+        <v>1024</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>343</v>
+        <v>1025</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>344</v>
+        <v>1026</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>345</v>
+        <v>1027</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>346</v>
+        <v>1028</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>347</v>
+        <v>1029</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>348</v>
+        <v>1030</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>349</v>
+        <v>1031</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>350</v>
+        <v>1032</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>351</v>
+        <v>1033</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>352</v>
+        <v>1034</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1302</v>
+        <v>1035</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.35</v>
+        <v>8.1</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.65</v>
+        <v>-0.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1303</v>
+        <v>1036</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>09:30 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.08</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-0.92</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1304</v>
+        <v>1037</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>09:30 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>07:00 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,34 +1030,24 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1305</v>
+        <v>1038</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1060,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1306</v>
+        <v>1039</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1307</v>
+        <v>1040</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>9.779999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="H19" t="n">
-        <v>0.78</v>
+        <v>-1.08</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1308</v>
+        <v>1041</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>9.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1309</v>
+        <v>1042</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>9</v>
       </c>
       <c r="G21" t="n">
-        <v>10.35</v>
+        <v>8.94</v>
       </c>
       <c r="H21" t="n">
-        <v>1.35</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1310</v>
+        <v>3782</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,16 +1218,26 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1240,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1311</v>
+        <v>3783</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1248,7 +1258,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1270,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1312</v>
+        <v>3784</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1278,26 +1288,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1313</v>
+        <v>3785</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,33 +1318,623 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3786</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>9</v>
+      </c>
+      <c r="G26" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3787</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3788</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3789</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3790</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3791</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3792</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>9</v>
+      </c>
+      <c r="G32" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>3793</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>08:30 AM</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>06:00 PM</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>9</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" t="n">
         <v>7.63</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H33" t="n">
         <v>-1.37</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3794</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>9</v>
+      </c>
+      <c r="G34" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>9</v>
+      </c>
+      <c r="G35" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>3796</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>3797</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>3798</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>3799</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>9</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3801</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -1391,13 +1981,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>64.41</v>
+        <v>114.87</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.59</v>
+        <v>-11.13</v>
       </c>
     </row>
     <row r="3">
@@ -1407,13 +1997,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>74.16</v>
+        <v>127.82</v>
       </c>
       <c r="D3" t="n">
-        <v>2.16</v>
+        <v>7.82</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,34 +1210,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3782</v>
+        <v>1043</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>8.35</v>
+        <v>4.62</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.65</v>
+        <v>-4.38</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3783</v>
+        <v>3782</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,16 +1258,26 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-0.65</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1280,7 +1290,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3784</v>
+        <v>3783</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,7 +1298,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1310,7 +1320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3785</v>
+        <v>3784</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1318,26 +1328,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3786</v>
+        <v>3785</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.1</v>
+        <v>9.75</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.75</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3787</v>
+        <v>3786</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1414,10 +1414,10 @@
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>9.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.78</v>
+        <v>0.1</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3788</v>
+        <v>3787</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9.699999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3789</v>
+        <v>3788</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>10.35</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>1.35</v>
+        <v>0.7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3790</v>
+        <v>3789</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1518,16 +1518,26 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46150</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>10.35</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,7 +1550,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3791</v>
+        <v>3790</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1548,7 +1558,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1570,7 +1580,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3792</v>
+        <v>3791</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1578,26 +1588,16 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3793</v>
+        <v>3792</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>7.63</v>
+        <v>9.5</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.37</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3794</v>
+        <v>3793</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>8.93</v>
+        <v>7.63</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.37</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3795</v>
+        <v>3794</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>8.949999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3796</v>
+        <v>3795</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1738,16 +1738,26 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.08</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>6.08</v>
+        <v>-0.05</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,7 +1770,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3797</v>
+        <v>3796</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1768,16 +1778,16 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46157</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>9.08</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1790,7 +1800,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3798</v>
+        <v>3797</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1798,7 +1808,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1820,7 +1830,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3799</v>
+        <v>3798</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1828,26 +1838,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>06:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>8.93</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3800</v>
+        <v>3799</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1884,10 +1884,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>8.6</v>
+        <v>8.93</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1900,41 +1900,121 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>3801</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>08:30 AM</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>06:00 PM</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>9</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" t="n">
         <v>9.17</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H42" t="n">
         <v>0.17</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>3802</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -1981,13 +2061,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>114.87</v>
+        <v>119.49</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.13</v>
+        <v>-15.51</v>
       </c>
     </row>
     <row r="3">
@@ -1997,13 +2077,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C3" t="n">
-        <v>127.82</v>
+        <v>132.74</v>
       </c>
       <c r="D3" t="n">
-        <v>7.82</v>
+        <v>3.74</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -1234,10 +1234,10 @@
         <v>9</v>
       </c>
       <c r="G22" t="n">
-        <v>4.62</v>
+        <v>8.82</v>
       </c>
       <c r="H22" t="n">
-        <v>-4.38</v>
+        <v>-0.18</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.92</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.08</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>119.49</v>
+        <v>123.69</v>
       </c>
       <c r="D2" t="n">
-        <v>-15.51</v>
+        <v>-11.31</v>
       </c>
     </row>
     <row r="3">
@@ -2080,10 +2080,10 @@
         <v>129</v>
       </c>
       <c r="C3" t="n">
-        <v>132.74</v>
+        <v>136.82</v>
       </c>
       <c r="D3" t="n">
-        <v>3.74</v>
+        <v>7.82</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1023</v>
+        <v>992</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1024</v>
+        <v>993</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1025</v>
+        <v>994</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1026</v>
+        <v>995</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1027</v>
+        <v>996</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1028</v>
+        <v>997</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1029</v>
+        <v>998</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1030</v>
+        <v>999</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1031</v>
+        <v>1000</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1032</v>
+        <v>1001</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1033</v>
+        <v>1002</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1034</v>
+        <v>1003</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1035</v>
+        <v>1004</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1036</v>
+        <v>1005</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1037</v>
+        <v>1006</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1038</v>
+        <v>1007</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1039</v>
+        <v>1008</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1040</v>
+        <v>1009</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1041</v>
+        <v>1010</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1042</v>
+        <v>1011</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1043</v>
+        <v>1012</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1250,34 +1250,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3782</v>
+        <v>1013</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46143</v>
+        <v>46164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>9</v>
       </c>
       <c r="G23" t="n">
-        <v>8.35</v>
+        <v>4.45</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.65</v>
+        <v>-4.55</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1290,15 +1290,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3783</v>
+        <v>1014</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1320,15 +1320,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3784</v>
+        <v>1015</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46145</v>
+        <v>46166</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1350,34 +1350,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3785</v>
+        <v>1016</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>9</v>
       </c>
       <c r="G26" t="n">
-        <v>9.75</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.75</v>
+        <v>-9</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1390,34 +1390,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3786</v>
+        <v>1017</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>9</v>
       </c>
       <c r="G27" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,34 +1430,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3787</v>
+        <v>1018</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>9.779999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="H28" t="n">
-        <v>0.78</v>
+        <v>-4.85</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1470,34 +1470,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3788</v>
+        <v>1019</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ZHANG, CECILIA [6608]</t>
+          <t>DIAZ, MARLENE A [6510]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>09:30 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>06:00 PM</t>
+          <t>07:00 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7</v>
+        <v>-9</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>3789</v>
+        <v>3782</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1534,10 +1534,10 @@
         <v>9</v>
       </c>
       <c r="G30" t="n">
-        <v>10.35</v>
+        <v>8.35</v>
       </c>
       <c r="H30" t="n">
-        <v>1.35</v>
+        <v>-0.65</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3790</v>
+        <v>3783</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46151</v>
+        <v>46144</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>3791</v>
+        <v>3784</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3792</v>
+        <v>3785</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1634,10 +1634,10 @@
         <v>9</v>
       </c>
       <c r="G33" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3793</v>
+        <v>3786</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         <v>9</v>
       </c>
       <c r="G34" t="n">
-        <v>7.63</v>
+        <v>9.1</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.37</v>
+        <v>0.1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3794</v>
+        <v>3787</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         <v>9</v>
       </c>
       <c r="G35" t="n">
-        <v>8.93</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3795</v>
+        <v>3788</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
         <v>9</v>
       </c>
       <c r="G36" t="n">
-        <v>8.949999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3796</v>
+        <v>3789</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1778,16 +1778,26 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>9.08</v>
+        <v>10.35</v>
       </c>
       <c r="H37" t="n">
-        <v>6.08</v>
+        <v>1.35</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1800,7 +1810,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3797</v>
+        <v>3790</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1808,7 +1818,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46158</v>
+        <v>46151</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1830,7 +1840,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3798</v>
+        <v>3791</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1838,7 +1848,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46159</v>
+        <v>46152</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1860,7 +1870,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3799</v>
+        <v>3792</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1868,7 +1878,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1884,10 +1894,10 @@
         <v>9</v>
       </c>
       <c r="G40" t="n">
-        <v>8.93</v>
+        <v>9.5</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1900,7 +1910,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3800</v>
+        <v>3793</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1908,7 +1918,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46161</v>
+        <v>46154</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1924,10 +1934,10 @@
         <v>9</v>
       </c>
       <c r="G41" t="n">
-        <v>8.6</v>
+        <v>7.63</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4</v>
+        <v>-1.37</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1940,7 +1950,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3801</v>
+        <v>3794</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1948,7 +1958,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1964,10 +1974,10 @@
         <v>9</v>
       </c>
       <c r="G42" t="n">
-        <v>9.17</v>
+        <v>8.93</v>
       </c>
       <c r="H42" t="n">
-        <v>0.17</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1980,41 +1990,551 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
+        <v>3795</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" t="n">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3796</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>3797</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>3798</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3799</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>9</v>
+      </c>
+      <c r="G47" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3800</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>9</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3801</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>9</v>
+      </c>
+      <c r="G49" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>3802</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>ZHANG, CECILIA [6608]</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>08:30 AM</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>06:00 PM</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>9</v>
-      </c>
-      <c r="G43" t="n">
-        <v>9</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Avat Construction &amp; Development</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
+      <c r="F50" t="n">
+        <v>9</v>
+      </c>
+      <c r="G50" t="n">
+        <v>9</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3803</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3804</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3805</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3806</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3807</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>9</v>
+      </c>
+      <c r="G55" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3808</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8611</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3809</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ZHANG, CECILIA [6608]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>06:00 PM</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Avat Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>8611</v>
       </c>
     </row>
@@ -2061,13 +2581,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>123.69</v>
+        <v>140.69</v>
       </c>
       <c r="D2" t="n">
-        <v>-11.31</v>
+        <v>-39.31</v>
       </c>
     </row>
     <row r="3">
@@ -2077,13 +2597,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>129</v>
+        <v>174</v>
       </c>
       <c r="C3" t="n">
-        <v>136.82</v>
+        <v>161.83</v>
       </c>
       <c r="D3" t="n">
-        <v>7.82</v>
+        <v>-12.17</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -1494,10 +1494,10 @@
         <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="H29" t="n">
-        <v>-9</v>
+        <v>-4.17</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2584,10 +2584,10 @@
         <v>180</v>
       </c>
       <c r="C2" t="n">
-        <v>140.69</v>
+        <v>145.52</v>
       </c>
       <c r="D2" t="n">
-        <v>-39.31</v>
+        <v>-34.48</v>
       </c>
     </row>
     <row r="3">

--- a/sheet/8611.xlsx
+++ b/sheet/8611.xlsx
@@ -2524,10 +2524,10 @@
         <v>9</v>
       </c>
       <c r="G57" t="n">
-        <v>4.73</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.27</v>
+        <v>0.38</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
         <v>174</v>
       </c>
       <c r="C3" t="n">
-        <v>161.83</v>
+        <v>166.48</v>
       </c>
       <c r="D3" t="n">
-        <v>-12.17</v>
+        <v>-7.52</v>
       </c>
     </row>
   </sheetData>
